--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487018_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487018_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.9111</v>
+        <v>3.2984</v>
       </c>
       <c r="E2" t="n">
-        <v>2.0089</v>
+        <v>1.7222</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9023</v>
+        <v>1.5762</v>
       </c>
       <c r="G2" t="n">
         <v>0.4727</v>
@@ -610,13 +610,13 @@
         <v>1.8481</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1469</v>
+        <v>-0.4658</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0114</v>
+        <v>-0.2753</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1356</v>
+        <v>-0.1905</v>
       </c>
       <c r="V2" t="n">
         <v>3.4969</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6968</v>
+        <v>3.2205</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1393</v>
+        <v>2.3369</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5575</v>
+        <v>0.8836000000000001</v>
       </c>
       <c r="G3" t="n">
         <v>0.3245</v>
@@ -688,13 +688,13 @@
         <v>2.2588</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0384</v>
+        <v>0.4853</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4144</v>
+        <v>0.612</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4527</v>
+        <v>-0.1267</v>
       </c>
       <c r="V3" t="n">
         <v>1.1786</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5145</v>
+        <v>1.7324</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.524</v>
+        <v>0.1307</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0385</v>
+        <v>1.6017</v>
       </c>
       <c r="G4" t="n">
         <v>0.4482</v>
@@ -766,13 +766,13 @@
         <v>2.2588</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.9337</v>
+        <v>-0.7158</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6124000000000001</v>
+        <v>0.0424</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.3214</v>
+        <v>-0.7581</v>
       </c>
       <c r="V4" t="n">
         <v>0.768</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. LAROUSSE</t>
+          <t>P. SALA VALLMAJO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0032</v>
+        <v>-0.734</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.512</v>
+        <v>2.235</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5088</v>
+        <v>-2.969</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.5887</v>
+        <v>0.9036</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4608</v>
+        <v>-0.3279</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.0495</v>
+        <v>1.2315</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8283</v>
+        <v>2.421</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7889</v>
+        <v>0.4477</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0395</v>
+        <v>1.9733</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.4171</v>
+        <v>-1.5174</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3281</v>
+        <v>-0.7756</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.089</v>
+        <v>-0.7418</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.6694</v>
+        <v>1.6427</v>
       </c>
       <c r="Q5" t="n">
-        <v>-4.1068</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4374</v>
+        <v>1.6427</v>
       </c>
       <c r="S5" t="n">
-        <v>2.5343</v>
+        <v>-0.923</v>
       </c>
       <c r="T5" t="n">
-        <v>1.0458</v>
+        <v>-0.186</v>
       </c>
       <c r="U5" t="n">
-        <v>1.4885</v>
+        <v>-0.737</v>
       </c>
       <c r="V5" t="n">
-        <v>0.7207</v>
+        <v>-2.3573</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7207</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-2.3573</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. SALA VALLMAJO</t>
+          <t>F. ADEBAYO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.9728</v>
+        <v>-0.9369</v>
       </c>
       <c r="E6" t="n">
-        <v>2.0258</v>
+        <v>-3.0374</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.9986</v>
+        <v>2.1005</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9036</v>
+        <v>-1.3641</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3279</v>
+        <v>-0.9564</v>
       </c>
       <c r="I6" t="n">
-        <v>1.2315</v>
+        <v>-0.4077</v>
       </c>
       <c r="J6" t="n">
-        <v>2.421</v>
+        <v>-0.9838</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4477</v>
+        <v>-0.852</v>
       </c>
       <c r="L6" t="n">
-        <v>1.9733</v>
+        <v>-0.1318</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.5174</v>
+        <v>-0.3803</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7756</v>
+        <v>-0.1044</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7418</v>
+        <v>-0.2759</v>
       </c>
       <c r="P6" t="n">
-        <v>1.6427</v>
+        <v>-1.6427</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-3.0801</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6427</v>
+        <v>1.4374</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.1619</v>
+        <v>0.5813</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3952</v>
+        <v>0.06569999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7665999999999999</v>
+        <v>0.5155999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.3573</v>
+        <v>1.4887</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.9609</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.3573</v>
+        <v>0.5276999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. EFAMBE</t>
+          <t>C. LAROUSSE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0699</v>
+        <v>-1.101</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8117</v>
+        <v>-2.0466</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.8816</v>
+        <v>0.9456</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.8957</v>
+        <v>-0.5887</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3436</v>
+        <v>0.4608</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.5522</v>
+        <v>-1.0495</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2454</v>
+        <v>0.8283</v>
       </c>
       <c r="K7" t="n">
-        <v>0.127</v>
+        <v>0.7889</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1184</v>
+        <v>0.0395</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.1412</v>
+        <v>-1.4171</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4706</v>
+        <v>-0.3281</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.6706</v>
+        <v>-1.089</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.8481</v>
+        <v>-2.6694</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.0801</v>
+        <v>-4.1068</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2321</v>
+        <v>1.4374</v>
       </c>
       <c r="S7" t="n">
-        <v>2.3249</v>
+        <v>1.4365</v>
       </c>
       <c r="T7" t="n">
-        <v>2.4678</v>
+        <v>0.5112</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1429</v>
+        <v>0.9253</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3491</v>
+        <v>0.7207</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1786</v>
+        <v>0.7207</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.8295</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F. ADEBAYO</t>
+          <t>I. VALERA COROMINAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.7063</v>
+        <v>-2.0237</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.281</v>
+        <v>-0.3264</v>
       </c>
       <c r="F8" t="n">
-        <v>2.5747</v>
+        <v>-1.6973</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.3641</v>
+        <v>0.5112</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.9564</v>
+        <v>-0.1202</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4077</v>
+        <v>0.6315</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.9838</v>
+        <v>1.8364</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.852</v>
+        <v>0.6263</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.1318</v>
+        <v>1.21</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3803</v>
+        <v>-1.3251</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1044</v>
+        <v>-0.7465000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2759</v>
+        <v>-0.5786</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.6427</v>
+        <v>0.616</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.0801</v>
+        <v>-1.0267</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4374</v>
+        <v>1.6427</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1881</v>
+        <v>-1.4528</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.178</v>
+        <v>-0.4379</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9899</v>
+        <v>-1.0149</v>
       </c>
       <c r="V8" t="n">
-        <v>1.4887</v>
+        <v>-1.6981</v>
       </c>
       <c r="W8" t="n">
-        <v>0.9609</v>
+        <v>-0.6982</v>
       </c>
       <c r="X8" t="n">
-        <v>0.5276999999999999</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. VALERA COROMINAS</t>
+          <t>A. VILA I GÓMEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.4421</v>
+        <v>-2.3626</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7448</v>
+        <v>-1.8169</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.6973</v>
+        <v>-0.5457</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5112</v>
+        <v>-1.3029</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1202</v>
+        <v>-0.3504</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6315</v>
+        <v>-0.9525</v>
       </c>
       <c r="J9" t="n">
-        <v>1.8364</v>
+        <v>-0.6584</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6263</v>
+        <v>0.0389</v>
       </c>
       <c r="L9" t="n">
-        <v>1.21</v>
+        <v>-0.6974</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.3251</v>
+        <v>-0.6445</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7465000000000001</v>
+        <v>-0.3893</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5786</v>
+        <v>-0.2552</v>
       </c>
       <c r="P9" t="n">
-        <v>0.616</v>
+        <v>-1.0267</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6427</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.8713</v>
+        <v>-0.0329</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8563</v>
+        <v>-0.1317</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.0149</v>
+        <v>0.0988</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.6981</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.6982</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. VILA I GÓMEZ</t>
+          <t>D. EFAMBE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4877</v>
+        <v>-2.4388</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8827</v>
+        <v>-0.5869</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.605</v>
+        <v>-1.8519</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.3029</v>
+        <v>-1.8957</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3504</v>
+        <v>-0.3436</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9525</v>
+        <v>-1.5522</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6584</v>
+        <v>0.2454</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0389</v>
+        <v>0.127</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6974</v>
+        <v>0.1184</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6445</v>
+        <v>-2.1412</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3893</v>
+        <v>-0.4706</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2552</v>
+        <v>-1.6706</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.0267</v>
+        <v>-1.8481</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0267</v>
+        <v>-3.0801</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.2321</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1581</v>
+        <v>0.956</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1976</v>
+        <v>1.0692</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0395</v>
+        <v>-0.1132</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.3491</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.8295</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.2905</v>
+        <v>-2.5164</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7364</v>
+        <v>-1.318</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.5541</v>
+        <v>-1.1984</v>
       </c>
       <c r="G11" t="n">
         <v>-0.7963</v>
@@ -1312,13 +1312,13 @@
         <v>1.6427</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.1534</v>
+        <v>-1.3792</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8563</v>
+        <v>-0.4379</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.297</v>
+        <v>-0.9413</v>
       </c>
       <c r="V11" t="n">
         <v>0.0698</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.850099999999999</v>
+        <v>-3.8621</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.695199999999999</v>
+        <v>-2.7074</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.154800000000001</v>
+        <v>-1.1547</v>
       </c>
       <c r="G12" t="n">
         <v>-3.2875</v>
@@ -1369,7 +1369,7 @@
         <v>3.4267</v>
       </c>
       <c r="L12" t="n">
-        <v>4.7474</v>
+        <v>4.747400000000001</v>
       </c>
       <c r="M12" t="n">
         <v>-11.4618</v>
@@ -1378,7 +1378,7 @@
         <v>-4.399900000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>-7.0618</v>
+        <v>-7.061800000000001</v>
       </c>
       <c r="P12" t="n">
         <v>-3.08</v>
@@ -1390,10 +1390,10 @@
         <v>15.4007</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.4988</v>
+        <v>-1.5104</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1564</v>
+        <v>0.8316999999999999</v>
       </c>
       <c r="U12" t="n">
         <v>-2.342</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.924</v>
+        <v>5.8263</v>
       </c>
       <c r="E13" t="n">
         <v>5.5894</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3346</v>
+        <v>0.2369</v>
       </c>
       <c r="G13" t="n">
         <v>6.8999</v>
@@ -1468,13 +1468,13 @@
         <v>2.0534</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3866</v>
+        <v>-0.4843</v>
       </c>
       <c r="T13" t="n">
         <v>-0.4225</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0359</v>
+        <v>-0.0618</v>
       </c>
       <c r="V13" t="n">
         <v>-0.5893</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. LOPEZ-SANVICENTE RETA</t>
+          <t>O. BIESHAAR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.9065</v>
+        <v>2.381</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.0238</v>
+        <v>0.6649</v>
       </c>
       <c r="F14" t="n">
-        <v>2.9303</v>
+        <v>1.7161</v>
       </c>
       <c r="G14" t="n">
-        <v>1.644</v>
+        <v>-0.6059</v>
       </c>
       <c r="H14" t="n">
-        <v>2.2544</v>
+        <v>1.3072</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.6104000000000001</v>
+        <v>-1.9131</v>
       </c>
       <c r="J14" t="n">
-        <v>2.6036</v>
+        <v>0.2195</v>
       </c>
       <c r="K14" t="n">
-        <v>2.4722</v>
+        <v>0.9962</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1314</v>
+        <v>-0.7766999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.9596</v>
+        <v>-0.8254</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2177</v>
+        <v>0.311</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.7418</v>
+        <v>-1.1365</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.2053</v>
+        <v>1.8481</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>1.8481</v>
       </c>
       <c r="S14" t="n">
-        <v>1.8169</v>
+        <v>0.2005</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2249</v>
+        <v>0.2051</v>
       </c>
       <c r="U14" t="n">
-        <v>2.0418</v>
+        <v>-0.0047</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.3491</v>
+        <v>0.9384</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.3491</v>
+        <v>0.2402</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>0.6982</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>O. THIAM PEDRERA</t>
+          <t>P. LOPEZ-SANVICENTE RETA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.7393</v>
+        <v>2.2142</v>
       </c>
       <c r="E15" t="n">
-        <v>2.9757</v>
+        <v>0.4992</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2364</v>
+        <v>1.715</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.4029</v>
+        <v>1.644</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.716</v>
+        <v>2.2544</v>
       </c>
       <c r="I15" t="n">
-        <v>0.313</v>
+        <v>-0.6104000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.2173</v>
+        <v>2.6036</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.3879</v>
+        <v>2.4722</v>
       </c>
       <c r="L15" t="n">
-        <v>1.1706</v>
+        <v>0.1314</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.1856</v>
+        <v>-0.9596</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3281</v>
+        <v>-0.2177</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.8575</v>
+        <v>-0.7418</v>
       </c>
       <c r="P15" t="n">
-        <v>-0</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q15" t="n">
         <v>-2.0534</v>
       </c>
       <c r="R15" t="n">
-        <v>2.0534</v>
+        <v>1.8481</v>
       </c>
       <c r="S15" t="n">
-        <v>3.902</v>
+        <v>1.1246</v>
       </c>
       <c r="T15" t="n">
-        <v>3.8275</v>
+        <v>0.2982</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0745</v>
+        <v>0.8264</v>
       </c>
       <c r="V15" t="n">
-        <v>0.2402</v>
+        <v>-0.3491</v>
       </c>
       <c r="W15" t="n">
-        <v>1.4189</v>
+        <v>-0.3491</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>O. BIESHAAR</t>
+          <t>H. FIGUEROA ÁLVAREZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6052</v>
+        <v>1.8415</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0373</v>
+        <v>0.0304</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5679</v>
+        <v>1.8111</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.6059</v>
+        <v>0.5688</v>
       </c>
       <c r="H16" t="n">
-        <v>1.3072</v>
+        <v>1.4401</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.9131</v>
+        <v>-0.8713</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2195</v>
+        <v>0.7965</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9962</v>
+        <v>1.5996</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.7766999999999999</v>
+        <v>-0.8031</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8254</v>
+        <v>-0.2278</v>
       </c>
       <c r="N16" t="n">
-        <v>0.311</v>
+        <v>-0.1596</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.1365</v>
+        <v>-0.0682</v>
       </c>
       <c r="P16" t="n">
-        <v>1.8481</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R16" t="n">
         <v>1.8481</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5754</v>
+        <v>-0.7478</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4225</v>
+        <v>-0.4806</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1529</v>
+        <v>-0.2672</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9384</v>
+        <v>2.2259</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2402</v>
+        <v>1.7679</v>
       </c>
       <c r="X16" t="n">
-        <v>0.6982</v>
+        <v>0.4579</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>H. FIGUEROA ÁLVAREZ</t>
+          <t>O. THIAM PEDRERA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.391</v>
+        <v>0.8983</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.8064</v>
+        <v>0.779</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1973</v>
+        <v>0.1193</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5688</v>
+        <v>-1.4029</v>
       </c>
       <c r="H17" t="n">
-        <v>1.4401</v>
+        <v>-1.716</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8713</v>
+        <v>0.313</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7965</v>
+        <v>-0.2173</v>
       </c>
       <c r="K17" t="n">
-        <v>1.5996</v>
+        <v>-1.3879</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.8031</v>
+        <v>1.1706</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2278</v>
+        <v>-1.1856</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1596</v>
+        <v>-0.3281</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0682</v>
+        <v>-0.8575</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.2053</v>
+        <v>-0</v>
       </c>
       <c r="Q17" t="n">
         <v>-2.0534</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8481</v>
+        <v>2.0534</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.1983</v>
+        <v>2.061</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.3174</v>
+        <v>1.6309</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.8809</v>
+        <v>0.4302</v>
       </c>
       <c r="V17" t="n">
-        <v>2.2259</v>
+        <v>0.2402</v>
       </c>
       <c r="W17" t="n">
-        <v>1.7679</v>
+        <v>1.4189</v>
       </c>
       <c r="X17" t="n">
-        <v>0.4579</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2142</v>
+        <v>0.2718</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6486</v>
+        <v>0.4394</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4344</v>
+        <v>-0.1677</v>
       </c>
       <c r="G18" t="n">
         <v>-0.2731</v>
@@ -1858,13 +1858,13 @@
         <v>1.8481</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4954</v>
+        <v>0.553</v>
       </c>
       <c r="T18" t="n">
-        <v>0.736</v>
+        <v>0.5268</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2406</v>
+        <v>0.0262</v>
       </c>
       <c r="V18" t="n">
         <v>-0.8295</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. VAZQUEZ VALLEJO</t>
+          <t>A. SMITH</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9442</v>
+        <v>-0.4543</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1398</v>
+        <v>-0.8214</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0841</v>
+        <v>0.367</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.4803</v>
+        <v>-1.4306</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.9566</v>
+        <v>-2.7276</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4763</v>
+        <v>1.297</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3896</v>
+        <v>-0.1316</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.2944</v>
+        <v>-2.565</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6840000000000001</v>
+        <v>2.4335</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8699</v>
+        <v>-1.299</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6623</v>
+        <v>-0.1626</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2077</v>
+        <v>-1.1365</v>
       </c>
       <c r="P19" t="n">
-        <v>1.8481</v>
+        <v>1.2321</v>
       </c>
       <c r="Q19" t="n">
+        <v>-1.0267</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2.2588</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.2247</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.3369</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-0.1122</v>
+      </c>
+      <c r="V19" t="n">
+        <v>-0.4805</v>
+      </c>
+      <c r="W19" t="n">
         <v>0</v>
       </c>
-      <c r="R19" t="n">
-        <v>1.8481</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1.2014</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0.9064</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="V19" t="n">
-        <v>-3.5134</v>
-      </c>
-      <c r="W19" t="n">
-        <v>-1.1561</v>
-      </c>
       <c r="X19" t="n">
-        <v>-2.3573</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. SMITH</t>
+          <t>G. VAZQUEZ VALLEJO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3191</v>
+        <v>-1.5946</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.449</v>
+        <v>-0.3832</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1299</v>
+        <v>-1.2114</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.4306</v>
+        <v>-0.4803</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.7276</v>
+        <v>-0.9566</v>
       </c>
       <c r="I20" t="n">
-        <v>1.297</v>
+        <v>0.4763</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.1316</v>
+        <v>0.3896</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.565</v>
+        <v>-0.2944</v>
       </c>
       <c r="L20" t="n">
-        <v>2.4335</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.299</v>
+        <v>-0.8699</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1626</v>
+        <v>-0.6623</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.1365</v>
+        <v>-0.2077</v>
       </c>
       <c r="P20" t="n">
-        <v>1.2321</v>
+        <v>1.8481</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.2588</v>
+        <v>1.8481</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6401</v>
+        <v>0.5511</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2907</v>
+        <v>0.3833</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3494</v>
+        <v>0.1677</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.4805</v>
+        <v>-3.5134</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-1.1561</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.4805</v>
+        <v>-2.3573</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3761</v>
+        <v>-1.7736</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1062</v>
+        <v>-0.5246</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2699</v>
+        <v>-1.249</v>
       </c>
       <c r="G21" t="n">
         <v>0.4202</v>
@@ -2092,13 +2092,13 @@
         <v>1.4374</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4788</v>
+        <v>0.0813</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6042</v>
+        <v>0.1858</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1254</v>
+        <v>-0.1045</v>
       </c>
       <c r="V21" t="n">
         <v>-1.6591</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.2907</v>
+        <v>-4.0633</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.8508</v>
+        <v>-5.1185</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5601</v>
+        <v>1.0552</v>
       </c>
       <c r="G22" t="n">
         <v>-2.0525</v>
@@ -2170,13 +2170,13 @@
         <v>1.4374</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.5955</v>
+        <v>-0.3681</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.054</v>
+        <v>-0.3217</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5415</v>
+        <v>-0.0464</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>4.850099999999999</v>
+        <v>5.5473</v>
       </c>
       <c r="E23" t="n">
         <v>1.154600000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>3.6953</v>
+        <v>4.392499999999999</v>
       </c>
       <c r="G23" t="n">
         <v>3.287599999999999</v>
@@ -2218,16 +2218,16 @@
         <v>0.9733999999999994</v>
       </c>
       <c r="I23" t="n">
-        <v>2.314399999999999</v>
+        <v>2.3144</v>
       </c>
       <c r="J23" t="n">
         <v>11.4617</v>
       </c>
       <c r="K23" t="n">
-        <v>4.400099999999999</v>
+        <v>4.4001</v>
       </c>
       <c r="L23" t="n">
-        <v>7.061800000000002</v>
+        <v>7.0618</v>
       </c>
       <c r="M23" t="n">
         <v>-8.174099999999999</v>
@@ -2248,19 +2248,19 @@
         <v>18.4809</v>
       </c>
       <c r="S23" t="n">
-        <v>2.4986</v>
+        <v>3.196</v>
       </c>
       <c r="T23" t="n">
-        <v>2.3421</v>
+        <v>2.342200000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1564999999999998</v>
+        <v>0.8536999999999999</v>
       </c>
       <c r="V23" t="n">
         <v>-4.016399999999999</v>
       </c>
       <c r="W23" t="n">
-        <v>2.7513</v>
+        <v>2.751300000000001</v>
       </c>
       <c r="X23" t="n">
         <v>-6.767800000000001</v>
